--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -801,22 +801,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -859,40 +859,120 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>U.N.A.M.</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Atl. San Luis</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>23</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -975,22 +975,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -1033,22 +1033,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Juarez</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -1091,22 +1091,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -1149,40 +1149,120 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Club America</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tigres</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>

--- a/new-stats/club-leon.xlsx
+++ b/new-stats/club-leon.xlsx
@@ -1265,22 +1265,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
